--- a/data/externalStats/File1/RPT_RPT3271268520973PM_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT3271268520973PM_externalStats.xlsx
@@ -2063,7 +2063,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>4892930.933363182</v>
+        <v>4892930.933363181</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>7094.223987863294</v>
+        <v>7094.223987863295</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -2140,7 +2140,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774572</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -2255,10 +2255,10 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>556393.5809359539</v>
+        <v>556393.5809359541</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>827.1029214485164</v>
+        <v>827.1029214485163</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="AN28" s="58" t="n">
-        <v>3060.609005713498</v>
+        <v>3060.609005713499</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" thickBot="1">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>122337.3954337065</v>
+        <v>122337.3954337064</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>358.4698264140782</v>
+        <v>358.4698264140781</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -2777,7 +2777,7 @@
         <v>119720.1244139953</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>45.33514103688001</v>
+        <v>45.33514103688</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
         <v>77252.6286851506</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>278.6758692628374</v>
+        <v>278.6758692628373</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>69746.80722920313</v>
+        <v>69746.80722920311</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>203.9703763401057</v>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>69517.67772777993</v>
+        <v>69517.67772777994</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>194.3574113273374</v>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="AN43" s="58" t="n">
-        <v>977.238924089403</v>
+        <v>977.2389240894031</v>
       </c>
     </row>
     <row r="44" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.4948504607565</v>
+        <v>25.49485046075651</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -4415,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>0.6430482566932423</v>
+        <v>0.6430482566932424</v>
       </c>
       <c r="Z59" s="132" t="n">
         <v>31.69480265912987</v>
@@ -4472,7 +4472,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="130" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="K60" s="131" t="n">
         <v>0</v>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="132" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="P60" s="130" t="n">
         <v>6.618249046619539</v>
@@ -4553,7 +4553,7 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593554</v>
+        <v>6044.873869593555</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>3778.992897518413</v>
@@ -4571,7 +4571,7 @@
         <v>6228.776889941021</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.11454316705</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="AG61" s="122" t="n">
-        <v>74123.41884144765</v>
+        <v>74123.41884144767</v>
       </c>
       <c r="AH61" s="56" t="n">
         <v>334.3074243189063</v>
@@ -4634,10 +4634,10 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>4.363987808065344</v>
@@ -4649,7 +4649,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>695.6708181072372</v>
@@ -4664,7 +4664,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -4733,28 +4733,28 @@
         <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398546</v>
+        <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248006</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3718.424539440057</v>
+        <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178969</v>
+        <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472316</v>
+        <v>51.03255827472313</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>4661.350612147647</v>
+        <v>4661.350612147648</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>11601.99688704139</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>69529.4815161007</v>
+        <v>69529.48151610068</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>199.0707660676643</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -5048,22 +5048,22 @@
         <v>32665.80535718387</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>48404.11294602312</v>
+        <v>48404.11294602314</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575612</v>
+        <v>10340.41686575611</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -5075,7 +5075,7 @@
         <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>27700.89671012674</v>
+        <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>8009.429015133594</v>
@@ -5084,10 +5084,10 @@
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>36333.64374987039</v>
+        <v>36333.6437498704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -5126,10 +5126,10 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.1103028956</v>
+        <v>41792.11030289561</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>21604.37829025543</v>
+        <v>21604.37829025544</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>310.4568296744625</v>
@@ -5138,19 +5138,19 @@
         <v>4608.389429936386</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72370.99438301698</v>
+        <v>72370.99438301699</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436719</v>
+        <v>17647.25318436718</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>66413.06473054748</v>
@@ -5165,7 +5165,7 @@
         <v>248.6189656530615</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>5169.737606071402</v>
+        <v>5169.737606071404</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>64432.16393311792</v>
@@ -5762,10 +5762,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -5835,7 +5835,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -5902,10 +5902,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037885</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919335</v>
+        <v>2984.036659919333</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -6030,10 +6030,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.766737100835</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -6045,10 +6045,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -6097,10 +6097,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -6112,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -6369,7 +6369,7 @@
         <v>3985.486226866849</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009202</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -6384,10 +6384,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -6955,7 +6955,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303783</v>
+        <v>26.24432748303784</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904818</v>
+        <v>1.539423073904819</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -7010,7 +7010,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="130" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="K96" s="131" t="n">
         <v>0</v>
@@ -7022,7 +7022,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="132" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="P96" s="130" t="n">
         <v>26.57911917875575</v>
@@ -7040,7 +7040,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -7080,7 +7080,7 @@
         <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105204</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531614</v>
@@ -7110,7 +7110,7 @@
         <v>9058.982559296475</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>7214.103405258799</v>
+        <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>90.06841189161894</v>
@@ -7144,10 +7144,10 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>4.363987808065344</v>
@@ -7159,7 +7159,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>695.6708181072372</v>
@@ -7174,7 +7174,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -7214,16 +7214,16 @@
         <v>2715.313301741378</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>2139.409809914592</v>
+        <v>2139.40980991465</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982581</v>
+        <v>4701.938698982582</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9591.082297490615</v>
+        <v>9591.082297490673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>3197.258219982265</v>
@@ -7235,7 +7235,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144814</v>
+        <v>5099.728555144815</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -7250,7 +7250,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234371</v>
+        <v>5541.410161234373</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7317,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
     </row>
     <row r="101">
@@ -7492,7 +7492,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -7522,7 +7522,7 @@
         <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -7553,13 +7553,13 @@
         <v>283649.9563392566</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>271091.7847517669</v>
+        <v>271091.784751767</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079996</v>
+        <v>5255.414666079997</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -7589,7 +7589,7 @@
         <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>6050.693529975338</v>
+        <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>581216.5896308238</v>
@@ -8587,7 +8587,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>6251111.142429025</v>
+        <v>6251111.142429026</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>8867.763082677955</v>
+        <v>8867.763082677957</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -8664,7 +8664,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774572</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -8782,7 +8782,7 @@
         <v>634763.5969597776</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>926.3552720223385</v>
+        <v>926.3552720223383</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -8859,7 +8859,7 @@
         <v>432982.3623017127</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>747.2463417280801</v>
+        <v>747.2463417280802</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -9221,7 +9221,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>130915.3156911005</v>
+        <v>130915.3156911004</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>367.4459108674866</v>
@@ -9532,7 +9532,7 @@
         <v>81509.15863828435</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>291.5172533184688</v>
+        <v>291.5172533184689</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>72614.31094965676</v>
+        <v>72614.31094965678</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>147.4175985741262</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>69144.39120753238</v>
+        <v>69144.39120753236</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>116.7772917320124</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>6885874.739388803</v>
+        <v>6885874.739388804</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>15281.88969849521</v>
@@ -10852,7 +10852,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.4948504607565</v>
+        <v>25.49485046075651</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -10954,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>0.6430482566932423</v>
+        <v>0.6430482566932424</v>
       </c>
       <c r="Z59" s="132" t="n">
         <v>31.69480265912987</v>
@@ -10996,7 +10996,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="130" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="K60" s="131" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="132" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="P60" s="130" t="n">
         <v>6.618249046619539</v>
@@ -11077,7 +11077,7 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593554</v>
+        <v>6044.873869593555</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>3778.992897518413</v>
@@ -11095,7 +11095,7 @@
         <v>6228.776889941021</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.11454316705</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -11133,7 +11133,7 @@
         <v>79633.72037209972</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>212.4573984897524</v>
+        <v>212.4573984897525</v>
       </c>
     </row>
     <row r="62">
@@ -11158,10 +11158,10 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>4.363987808065344</v>
@@ -11173,7 +11173,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>695.6708181072372</v>
@@ -11188,7 +11188,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -11257,28 +11257,28 @@
         <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398546</v>
+        <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248006</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3718.424539440057</v>
+        <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178969</v>
+        <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472316</v>
+        <v>51.03255827472313</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>4661.350612147647</v>
+        <v>4661.350612147648</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>11601.99688704139</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11572,22 +11572,22 @@
         <v>32665.80535718387</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>48404.11294602312</v>
+        <v>48404.11294602314</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575612</v>
+        <v>10340.41686575611</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -11599,7 +11599,7 @@
         <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>27700.89671012674</v>
+        <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>8009.429015133594</v>
@@ -11608,10 +11608,10 @@
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>36333.64374987039</v>
+        <v>36333.6437498704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -11650,10 +11650,10 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.1103028956</v>
+        <v>41792.11030289561</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>21604.37829025543</v>
+        <v>21604.37829025544</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>310.4568296744625</v>
@@ -11662,19 +11662,19 @@
         <v>4608.389429936386</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72370.99438301698</v>
+        <v>72370.99438301699</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436719</v>
+        <v>17647.25318436718</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>66413.06473054748</v>
@@ -11689,7 +11689,7 @@
         <v>248.6189656530615</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>5169.737606071402</v>
+        <v>5169.737606071404</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>64432.16393311792</v>
@@ -12286,10 +12286,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -12301,10 +12301,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -12359,7 +12359,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -12426,10 +12426,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037885</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919335</v>
+        <v>2984.036659919333</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -12554,10 +12554,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.766737100835</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -12621,10 +12621,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -12636,10 +12636,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -12893,7 +12893,7 @@
         <v>3985.486226866849</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009202</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -12908,10 +12908,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13418,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -13467,7 +13467,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -13479,7 +13479,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303783</v>
+        <v>26.24432748303784</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -13491,7 +13491,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -13506,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904818</v>
+        <v>1.539423073904819</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -13534,7 +13534,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="130" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="K96" s="131" t="n">
         <v>0</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="132" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="P96" s="130" t="n">
         <v>26.57911917875575</v>
@@ -13564,7 +13564,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -13604,7 +13604,7 @@
         <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105204</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531614</v>
@@ -13634,7 +13634,7 @@
         <v>9058.982559296475</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>7214.103405258799</v>
+        <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>90.06841189161894</v>
@@ -13668,10 +13668,10 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>4.363987808065344</v>
@@ -13683,7 +13683,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>695.6708181072372</v>
@@ -13698,7 +13698,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -13738,16 +13738,16 @@
         <v>2715.313301741378</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>2139.409809914592</v>
+        <v>2139.40980991465</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982581</v>
+        <v>4701.938698982582</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9591.082297490615</v>
+        <v>9591.082297490673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>3197.258219982265</v>
@@ -13759,7 +13759,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144814</v>
+        <v>5099.728555144815</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -13774,7 +13774,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234371</v>
+        <v>5541.410161234373</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
     </row>
     <row r="101">
@@ -14016,7 +14016,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -14046,7 +14046,7 @@
         <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -14077,13 +14077,13 @@
         <v>283649.9563392566</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>271091.7847517669</v>
+        <v>271091.784751767</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079996</v>
+        <v>5255.414666079997</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -14113,7 +14113,7 @@
         <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>6050.693529975338</v>
+        <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>581216.5896308238</v>
@@ -15111,7 +15111,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7751805.56619507</v>
+        <v>7751805.566195068</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>10641.30259354557</v>
@@ -15168,7 +15168,7 @@
         </is>
       </c>
       <c r="AN25" s="48" t="n">
-        <v>5195.096501583942</v>
+        <v>5195.096501583941</v>
       </c>
     </row>
     <row r="26">
@@ -15188,7 +15188,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774572</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -15383,7 +15383,7 @@
         <v>453716.6716498772</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>747.6050199721097</v>
+        <v>747.6050199721096</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>198692.1838050455</v>
+        <v>198692.1838050454</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2035.572267133469</v>
@@ -15745,7 +15745,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>141906.6242620881</v>
+        <v>141906.624262088</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>376.6467564756085</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="AN34" s="58" t="n">
-        <v>29.56202142375364</v>
+        <v>29.56202142375365</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" thickBot="1">
@@ -15902,7 +15902,7 @@
         <v>138614.8865263913</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>48.16329992778643</v>
+        <v>48.16329992778642</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>77595.17294414854</v>
+        <v>77595.17294414852</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>199.9598321495294</v>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>63144.63416840847</v>
+        <v>63144.63416840845</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>158.3819594713257</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>212443.9720813232</v>
+        <v>212443.9720813231</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>2208.371887906786</v>
@@ -17376,7 +17376,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -17439,7 +17439,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -17451,7 +17451,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.4948504607565</v>
+        <v>25.49485046075651</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -17463,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>0.6430482566932423</v>
+        <v>0.6430482566932424</v>
       </c>
       <c r="Z59" s="132" t="n">
         <v>31.69480265912987</v>
@@ -17520,7 +17520,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="130" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="K60" s="131" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="132" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="P60" s="130" t="n">
         <v>6.618249046619539</v>
@@ -17601,7 +17601,7 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593554</v>
+        <v>6044.873869593555</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>3778.992897518413</v>
@@ -17619,7 +17619,7 @@
         <v>6228.776889941021</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.11454316705</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -17682,10 +17682,10 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>4.363987808065344</v>
@@ -17697,7 +17697,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>695.6708181072372</v>
@@ -17712,7 +17712,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -17781,28 +17781,28 @@
         <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398546</v>
+        <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248006</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3718.424539440057</v>
+        <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178969</v>
+        <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472316</v>
+        <v>51.03255827472313</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>4661.350612147647</v>
+        <v>4661.350612147648</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>11601.99688704139</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -18096,22 +18096,22 @@
         <v>32665.80535718387</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>48404.11294602312</v>
+        <v>48404.11294602314</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575612</v>
+        <v>10340.41686575611</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -18123,7 +18123,7 @@
         <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>27700.89671012674</v>
+        <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>8009.429015133594</v>
@@ -18132,10 +18132,10 @@
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>36333.64374987039</v>
+        <v>36333.6437498704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>36554.73731701937</v>
+        <v>36554.73731701936</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>63.56123947609333</v>
@@ -18174,10 +18174,10 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.1103028956</v>
+        <v>41792.11030289561</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>21604.37829025543</v>
+        <v>21604.37829025544</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>310.4568296744625</v>
@@ -18186,19 +18186,19 @@
         <v>4608.389429936386</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72370.99438301698</v>
+        <v>72370.99438301699</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436719</v>
+        <v>17647.25318436718</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>66413.06473054748</v>
@@ -18213,7 +18213,7 @@
         <v>248.6189656530615</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>5169.737606071402</v>
+        <v>5169.737606071404</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>64432.16393311792</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -18825,10 +18825,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -18883,7 +18883,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -18895,7 +18895,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -18950,10 +18950,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037885</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919335</v>
+        <v>2984.036659919333</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -18962,7 +18962,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -19078,10 +19078,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.766737100835</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -19145,10 +19145,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -19417,7 +19417,7 @@
         <v>3985.486226866849</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009202</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -19432,10 +19432,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19942,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -19991,7 +19991,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -20003,7 +20003,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303783</v>
+        <v>26.24432748303784</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -20015,7 +20015,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -20030,7 +20030,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904818</v>
+        <v>1.539423073904819</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -20058,7 +20058,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="130" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="K96" s="131" t="n">
         <v>0</v>
@@ -20070,7 +20070,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="132" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="P96" s="130" t="n">
         <v>26.57911917875575</v>
@@ -20088,7 +20088,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -20100,7 +20100,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -20128,7 +20128,7 @@
         <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105204</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531614</v>
@@ -20158,7 +20158,7 @@
         <v>9058.982559296475</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>7214.103405258799</v>
+        <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>90.06841189161894</v>
@@ -20192,10 +20192,10 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>4.363987808065344</v>
@@ -20207,7 +20207,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>695.6708181072372</v>
@@ -20222,7 +20222,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -20262,16 +20262,16 @@
         <v>2715.313301741378</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>2139.409809914592</v>
+        <v>2139.40980991465</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982581</v>
+        <v>4701.938698982582</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9591.082297490615</v>
+        <v>9591.082297490673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>3197.258219982265</v>
@@ -20283,7 +20283,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144814</v>
+        <v>5099.728555144815</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -20298,7 +20298,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234371</v>
+        <v>5541.410161234373</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20365,10 +20365,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
     </row>
     <row r="101">
@@ -20540,7 +20540,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -20570,7 +20570,7 @@
         <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -20601,13 +20601,13 @@
         <v>283649.9563392566</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>271091.7847517669</v>
+        <v>271091.784751767</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079996</v>
+        <v>5255.414666079997</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -20637,7 +20637,7 @@
         <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>6050.693529975338</v>
+        <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>581216.5896308238</v>
@@ -21635,7 +21635,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>9527427.014243348</v>
+        <v>9527427.014243346</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>12769.54856496323</v>
@@ -21712,7 +21712,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774572</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -21907,7 +21907,7 @@
         <v>467965.6858161185</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>745.1977318077994</v>
+        <v>745.1977318077995</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -22269,10 +22269,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>152313.3435365351</v>
+        <v>152313.343536535</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>386.0779912577577</v>
+        <v>386.0779912577576</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -22349,7 +22349,7 @@
         <v>148081.8312437994</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>49.50464783077527</v>
+        <v>49.50464783077526</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -22938,7 +22938,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>66764.26703950249</v>
+        <v>66764.26703950248</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>59.25783071991072</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>62060.39210193272</v>
+        <v>62060.39210193273</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>62.77817334161035</v>
@@ -23092,10 +23092,10 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>59901.00586583804</v>
+        <v>59901.00586583806</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>140.1553635753656</v>
+        <v>140.1553635753655</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>467965.6858161184</v>
+        <v>467965.6858161185</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>767.6697553968106</v>
@@ -23530,7 +23530,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>398214.3020311438</v>
+        <v>398214.3020311437</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>626.1720366637545</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>180624.6572362439</v>
+        <v>180624.657236244</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>416.1816363077455</v>
@@ -23695,7 +23695,7 @@
         <v>177023.5109933398</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>1554.212666503537</v>
+        <v>1554.212666503536</v>
       </c>
     </row>
     <row r="56">
@@ -23900,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -23963,7 +23963,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -23975,7 +23975,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.4948504607565</v>
+        <v>25.49485046075651</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -23987,7 +23987,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -24002,7 +24002,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>0.6430482566932423</v>
+        <v>0.6430482566932424</v>
       </c>
       <c r="Z59" s="132" t="n">
         <v>31.69480265912987</v>
@@ -24044,7 +24044,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="130" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="K60" s="131" t="n">
         <v>0</v>
@@ -24056,7 +24056,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="132" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="P60" s="130" t="n">
         <v>6.618249046619539</v>
@@ -24125,7 +24125,7 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593554</v>
+        <v>6044.873869593555</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>3778.992897518413</v>
@@ -24143,7 +24143,7 @@
         <v>6228.776889941021</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.11454316705</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -24206,10 +24206,10 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>4.363987808065344</v>
@@ -24221,7 +24221,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>695.6708181072372</v>
@@ -24236,7 +24236,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -24305,28 +24305,28 @@
         <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398546</v>
+        <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248006</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3718.424539440057</v>
+        <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178969</v>
+        <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472316</v>
+        <v>51.03255827472313</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>4661.350612147647</v>
+        <v>4661.350612147648</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>11601.99688704139</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24510,7 +24510,7 @@
         <v>35382.45525520735</v>
       </c>
       <c r="AH65" s="56" t="n">
-        <v>57.89489579250349</v>
+        <v>57.8948957925035</v>
       </c>
     </row>
     <row r="66">
@@ -24620,22 +24620,22 @@
         <v>32665.80535718387</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>48404.11294602312</v>
+        <v>48404.11294602314</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575612</v>
+        <v>10340.41686575611</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -24647,7 +24647,7 @@
         <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>27700.89671012674</v>
+        <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>8009.429015133594</v>
@@ -24656,10 +24656,10 @@
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>36333.64374987039</v>
+        <v>36333.6437498704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -24698,10 +24698,10 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.1103028956</v>
+        <v>41792.11030289561</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>21604.37829025543</v>
+        <v>21604.37829025544</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>310.4568296744625</v>
@@ -24710,19 +24710,19 @@
         <v>4608.389429936386</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72370.99438301698</v>
+        <v>72370.99438301699</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436719</v>
+        <v>17647.25318436718</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>66413.06473054748</v>
@@ -24737,7 +24737,7 @@
         <v>248.6189656530615</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>5169.737606071402</v>
+        <v>5169.737606071404</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>64432.16393311792</v>
@@ -25334,10 +25334,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -25349,10 +25349,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -25407,7 +25407,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -25419,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -25474,10 +25474,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037885</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919335</v>
+        <v>2984.036659919333</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -25486,7 +25486,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -25602,10 +25602,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.766737100835</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -25617,10 +25617,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -25669,10 +25669,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -25684,10 +25684,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -25941,7 +25941,7 @@
         <v>3985.486226866849</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009202</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -25956,10 +25956,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26466,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -26475,7 +26475,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -26515,7 +26515,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -26527,7 +26527,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303783</v>
+        <v>26.24432748303784</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -26539,7 +26539,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -26554,7 +26554,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904818</v>
+        <v>1.539423073904819</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -26582,7 +26582,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="130" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="K96" s="131" t="n">
         <v>0</v>
@@ -26594,7 +26594,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="132" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="P96" s="130" t="n">
         <v>26.57911917875575</v>
@@ -26612,7 +26612,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -26624,7 +26624,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -26652,7 +26652,7 @@
         <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105204</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531614</v>
@@ -26682,7 +26682,7 @@
         <v>9058.982559296475</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>7214.103405258799</v>
+        <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>90.06841189161894</v>
@@ -26716,10 +26716,10 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>4.363987808065344</v>
@@ -26731,7 +26731,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>695.6708181072372</v>
@@ -26746,7 +26746,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -26786,16 +26786,16 @@
         <v>2715.313301741378</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>2139.409809914592</v>
+        <v>2139.40980991465</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982581</v>
+        <v>4701.938698982582</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9591.082297490615</v>
+        <v>9591.082297490673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>3197.258219982265</v>
@@ -26807,7 +26807,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144814</v>
+        <v>5099.728555144815</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -26822,7 +26822,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234371</v>
+        <v>5541.410161234373</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
     </row>
     <row r="101">
@@ -27064,7 +27064,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -27094,7 +27094,7 @@
         <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -27125,13 +27125,13 @@
         <v>283649.9563392566</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>271091.7847517669</v>
+        <v>271091.784751767</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079996</v>
+        <v>5255.414666079997</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -27161,7 +27161,7 @@
         <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>6050.693529975338</v>
+        <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>581216.5896308238</v>
@@ -28159,7 +28159,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -28236,7 +28236,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774572</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>951956.7819181825</v>
+        <v>951956.7819181826</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1266.912187031183</v>
@@ -28431,7 +28431,7 @@
         <v>487821.5139308685</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>742.7981951113784</v>
+        <v>742.7981951113785</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -28645,7 +28645,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>159886.4982688307</v>
+        <v>159886.4982688306</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>50.88335227286235</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>121130.6189115225</v>
+        <v>121130.6189115226</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>165.4086408833709</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>86247.72213164017</v>
+        <v>86247.72213164018</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>196.0281448252941</v>
@@ -29388,7 +29388,7 @@
         <v>66969.5451954349</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>56.49108260359808</v>
+        <v>56.49108260359809</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -29462,7 +29462,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>57430.9172970456</v>
+        <v>57430.91729704559</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>124.0262843351125</v>
@@ -30424,7 +30424,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -30433,7 +30433,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -30487,7 +30487,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -30499,7 +30499,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.4948504607565</v>
+        <v>25.49485046075651</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -30511,7 +30511,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899804</v>
+        <v>0.6107794764899805</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -30526,7 +30526,7 @@
         <v>0</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>0.6430482566932423</v>
+        <v>0.6430482566932424</v>
       </c>
       <c r="Z59" s="132" t="n">
         <v>31.69480265912987</v>
@@ -30568,7 +30568,7 @@
         <v>11</v>
       </c>
       <c r="J60" s="130" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="K60" s="131" t="n">
         <v>0</v>
@@ -30580,7 +30580,7 @@
         <v>0</v>
       </c>
       <c r="N60" s="132" t="n">
-        <v>12.15752497820848</v>
+        <v>12.15752497820849</v>
       </c>
       <c r="P60" s="130" t="n">
         <v>6.618249046619539</v>
@@ -30649,7 +30649,7 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593554</v>
+        <v>6044.873869593555</v>
       </c>
       <c r="K61" s="131" t="n">
         <v>3778.992897518413</v>
@@ -30667,7 +30667,7 @@
         <v>6228.776889941021</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.11454316705</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -30730,10 +30730,10 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L62" s="131" t="n">
         <v>4.363987808065344</v>
@@ -30745,7 +30745,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
         <v>695.6708181072372</v>
@@ -30760,7 +30760,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
         <v>693.7423997998152</v>
@@ -30829,28 +30829,28 @@
         <v>3161.627253255683</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>2604.953328398546</v>
+        <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248006</v>
+        <v>42.03577551248009</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770583</v>
+        <v>4367.592784770584</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>3718.424539440057</v>
+        <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178969</v>
+        <v>3171.189177178967</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>51.03255827472316</v>
+        <v>51.03255827472313</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>4661.350612147647</v>
+        <v>4661.350612147648</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>11601.99688704139</v>
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582866</v>
+        <v>4367.589286582867</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -30931,10 +30931,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>4661.347007650006</v>
+        <v>4661.347007650007</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -31144,22 +31144,22 @@
         <v>32665.80535718387</v>
       </c>
       <c r="K67" s="140" t="n">
-        <v>14983.8247713327</v>
+        <v>14983.82477133271</v>
       </c>
       <c r="L67" s="140" t="n">
         <v>202.3739864950116</v>
       </c>
       <c r="M67" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>48404.11294602312</v>
+        <v>48404.11294602314</v>
       </c>
       <c r="P67" s="139" t="n">
         <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575612</v>
+        <v>10340.41686575611</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -31171,7 +31171,7 @@
         <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>27700.89671012674</v>
+        <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>8009.429015133594</v>
@@ -31180,10 +31180,10 @@
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>36333.64374987039</v>
+        <v>36333.6437498704</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -31222,10 +31222,10 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.1103028956</v>
+        <v>41792.11030289561</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>21604.37829025543</v>
+        <v>21604.37829025544</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>310.4568296744625</v>
@@ -31234,19 +31234,19 @@
         <v>4608.389429936386</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>72370.99438301698</v>
+        <v>72370.99438301699</v>
       </c>
       <c r="P68" s="142" t="n">
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436719</v>
+        <v>17647.25318436718</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>262.2537546686801</v>
+        <v>262.2537546686802</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133305</v>
+        <v>4897.646982133306</v>
       </c>
       <c r="T68" s="144" t="n">
         <v>66413.06473054748</v>
@@ -31261,7 +31261,7 @@
         <v>248.6189656530615</v>
       </c>
       <c r="Y68" s="143" t="n">
-        <v>5169.737606071402</v>
+        <v>5169.737606071404</v>
       </c>
       <c r="Z68" s="144" t="n">
         <v>64432.16393311792</v>
@@ -31858,10 +31858,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883199</v>
+        <v>0.8356985266883201</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -31873,10 +31873,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115763</v>
+        <v>0.8963748172115764</v>
       </c>
     </row>
     <row r="78">
@@ -31931,7 +31931,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -31943,7 +31943,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -31998,10 +31998,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037885</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919335</v>
+        <v>2984.036659919333</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -32010,7 +32010,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220914</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -32126,10 +32126,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.766737100835</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -32141,10 +32141,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.776397082107</v>
+        <v>933.7763970821072</v>
       </c>
     </row>
     <row r="82">
@@ -32193,10 +32193,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742318</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -32208,10 +32208,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867236</v>
+        <v>880.0595490867238</v>
       </c>
     </row>
     <row r="83">
@@ -32465,7 +32465,7 @@
         <v>3985.486226866849</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009202</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -32480,10 +32480,10 @@
         <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039352</v>
+        <v>880.9559239039354</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32990,7 +32990,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -32999,7 +32999,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.097628938235432</v>
+        <v>7.09762893823543</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -33039,7 +33039,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716617</v>
+        <v>24.87719139716618</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -33051,7 +33051,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303783</v>
+        <v>26.24432748303784</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -33063,7 +33063,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.4464780031783</v>
+        <v>1.446478003178301</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -33078,7 +33078,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904818</v>
+        <v>1.539423073904819</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -33106,7 +33106,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="130" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="K96" s="131" t="n">
         <v>0</v>
@@ -33118,7 +33118,7 @@
         <v>0</v>
       </c>
       <c r="N96" s="132" t="n">
-        <v>26.24935302529743</v>
+        <v>26.24935302529744</v>
       </c>
       <c r="P96" s="130" t="n">
         <v>26.57911917875575</v>
@@ -33136,7 +33136,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -33148,7 +33148,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -33176,7 +33176,7 @@
         <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105204</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531614</v>
@@ -33206,7 +33206,7 @@
         <v>9058.982559296475</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>7214.103405258799</v>
+        <v>7214.103405258798</v>
       </c>
       <c r="X97" s="131" t="n">
         <v>90.06841189161894</v>
@@ -33240,10 +33240,10 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386028</v>
+        <v>351.9287478386029</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.2653220010801</v>
+        <v>695.26532200108</v>
       </c>
       <c r="L98" s="131" t="n">
         <v>4.363987808065344</v>
@@ -33255,7 +33255,7 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
         <v>695.6708181072372</v>
@@ -33270,7 +33270,7 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
         <v>693.7423997998152</v>
@@ -33310,16 +33310,16 @@
         <v>2715.313301741378</v>
       </c>
       <c r="K99" s="131" t="n">
-        <v>2139.409809914592</v>
+        <v>2139.40980991465</v>
       </c>
       <c r="L99" s="131" t="n">
         <v>34.42048685206373</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>4701.938698982581</v>
+        <v>4701.938698982582</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9591.082297490615</v>
+        <v>9591.082297490673</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>3197.258219982265</v>
@@ -33331,7 +33331,7 @@
         <v>42.03577551248054</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144814</v>
+        <v>5099.728555144815</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -33346,7 +33346,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234371</v>
+        <v>5541.410161234373</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957098</v>
+        <v>5099.725056957099</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33413,10 +33413,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>5541.40655673673</v>
+        <v>5541.406556736731</v>
       </c>
     </row>
     <row r="101">
@@ -33588,7 +33588,7 @@
         <v>4086.411781183353</v>
       </c>
       <c r="M103" s="140" t="n">
-        <v>552.1088310115437</v>
+        <v>552.1088310115438</v>
       </c>
       <c r="N103" s="141" t="n">
         <v>538270.4316285335</v>
@@ -33618,7 +33618,7 @@
         <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670621</v>
+        <v>507.7439456670622</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -33649,13 +33649,13 @@
         <v>283649.9563392566</v>
       </c>
       <c r="K104" s="143" t="n">
-        <v>271091.7847517669</v>
+        <v>271091.784751767</v>
       </c>
       <c r="L104" s="143" t="n">
         <v>4206.317514998797</v>
       </c>
       <c r="M104" s="143" t="n">
-        <v>5255.414666079996</v>
+        <v>5255.414666079997</v>
       </c>
       <c r="N104" s="144" t="n">
         <v>568905.4085614788</v>
@@ -33685,7 +33685,7 @@
         <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>6050.693529975338</v>
+        <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>581216.5896308238</v>
